--- a/templates/sample-population.xlsx
+++ b/templates/sample-population.xlsx
@@ -4,7 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Osoby" sheetId="1" r:id="rId1"/>
-    <sheet name="Metadata" sheetId="2" r:id="rId2"/>
+    <sheet name="Nápověda" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -400,15 +400,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J21"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="30.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="5.83203125" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="32.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
     <col min="10" max="10" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -417,31 +417,31 @@
         <v>ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Vek</v>
+        <v>Věk</v>
       </c>
       <c r="C1" t="str">
-        <v>Pohlavi</v>
+        <v>Pohlaví</v>
       </c>
       <c r="D1" t="str">
-        <v>Vzdelani</v>
+        <v>Vzdělání</v>
       </c>
       <c r="E1" t="str">
-        <v>RodinnyStav</v>
+        <v>Stav</v>
       </c>
       <c r="F1" t="str">
-        <v>MaPartnera</v>
+        <v>Partner</v>
       </c>
       <c r="G1" t="str">
-        <v>ZaměstnaneckyStatus</v>
+        <v>Status</v>
       </c>
       <c r="H1" t="str">
-        <v>PrijmoveRozpeti</v>
+        <v>Příjem</v>
       </c>
       <c r="I1" t="str">
         <v>Kraj</v>
       </c>
       <c r="J1" t="str">
-        <v>ZivotniPribeh</v>
+        <v>Životní příběh</v>
       </c>
     </row>
     <row r="2">
@@ -458,7 +458,7 @@
         <v>Vysokoškolské</v>
       </c>
       <c r="E2" t="str">
-        <v>Ženatý/Vdaná</v>
+        <v>Svobodný/á</v>
       </c>
       <c r="F2" t="str">
         <v>Ano</v>
@@ -467,13 +467,13 @@
         <v>Zaměstnaný/á</v>
       </c>
       <c r="H2" t="str">
-        <v>Střední</v>
+        <v>Spíše vyšší</v>
       </c>
       <c r="I2" t="str">
         <v>Praha</v>
       </c>
       <c r="J2" t="str">
-        <v>Vystudoval ekonomii na VŠE, pracuje jako finanční analytik v nadnárodní firmě. Žije v Praze s manželkou a dvěma dětmi. Politicky se považuje za středopravicového.</v>
+        <v>Vystudoval informatiku na ČVUT. Pracuje jako softwarový inženýr v pražském startupu. Ve volném čase rád čte a chodí na výlety do přírody.</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +481,7 @@
         <v>P002</v>
       </c>
       <c r="B3">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C3" t="str">
         <v>Žena</v>
@@ -499,13 +499,13 @@
         <v>Důchodce/kyně</v>
       </c>
       <c r="H3" t="str">
-        <v>Nízký</v>
+        <v>Střední</v>
       </c>
       <c r="I3" t="str">
-        <v>Moravskoslezský</v>
+        <v>Jihomoravský</v>
       </c>
       <c r="J3" t="str">
-        <v>Celý život pracovala jako zdravotní sestra v ostravské nemocnici. Ovdověla před třemi lety, bydlí sama v panelákovém bytě. Ráda zahradničí a sleduje seriály.</v>
+        <v>Celý život pracovala jako účetní. Po odchodu do důchodu se věnuje zahrádkaření a vnoučatům.</v>
       </c>
     </row>
     <row r="4">
@@ -513,28 +513,28 @@
         <v>P003</v>
       </c>
       <c r="B4">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C4" t="str">
-        <v>Žena</v>
+        <v>Muž</v>
       </c>
       <c r="D4" t="str">
-        <v>S maturitou</v>
+        <v>Vyučení</v>
       </c>
       <c r="E4" t="str">
-        <v>Svobodný/á</v>
+        <v>Ženatý/Vdaná</v>
       </c>
       <c r="F4" t="str">
         <v>Ano</v>
       </c>
       <c r="G4" t="str">
-        <v>Student/ka</v>
+        <v>Zaměstnaný/á</v>
       </c>
       <c r="H4" t="str">
-        <v>Nízký</v>
+        <v>Střední</v>
       </c>
       <c r="I4" t="str">
-        <v>Jihomoravský</v>
+        <v>Moravskoslezský</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,28 +545,28 @@
         <v>P004</v>
       </c>
       <c r="B5">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C5" t="str">
-        <v>Muž</v>
+        <v>Žena</v>
       </c>
       <c r="D5" t="str">
-        <v>Vyučení</v>
+        <v>Vysokoškolské</v>
       </c>
       <c r="E5" t="str">
-        <v>Rozvedený/á</v>
+        <v>Svobodný/á</v>
       </c>
       <c r="F5" t="str">
-        <v>Ne</v>
+        <v>Ano</v>
       </c>
       <c r="G5" t="str">
         <v>Zaměstnaný/á</v>
       </c>
       <c r="H5" t="str">
-        <v>Spíše nižší</v>
+        <v>Nízký</v>
       </c>
       <c r="I5" t="str">
-        <v>Ústecký</v>
+        <v>Praha</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -577,13 +577,13 @@
         <v>P005</v>
       </c>
       <c r="B6">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C6" t="str">
-        <v>Žena</v>
+        <v>Muž</v>
       </c>
       <c r="D6" t="str">
-        <v>Vysokoškolské</v>
+        <v>S maturitou</v>
       </c>
       <c r="E6" t="str">
         <v>Ženatý/Vdaná</v>
@@ -592,10 +592,10 @@
         <v>Ano</v>
       </c>
       <c r="G6" t="str">
-        <v>Mateřská/rodičovská dovolená</v>
+        <v>Důchodce/kyně</v>
       </c>
       <c r="H6" t="str">
-        <v>Spíše vyšší</v>
+        <v>Spíše nižší</v>
       </c>
       <c r="I6" t="str">
         <v>Středočeský</v>
@@ -609,28 +609,28 @@
         <v>P006</v>
       </c>
       <c r="B7">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C7" t="str">
-        <v>Muž</v>
+        <v>Žena</v>
       </c>
       <c r="D7" t="str">
-        <v>Vysokoškolské</v>
+        <v>Vyšší odborné</v>
       </c>
       <c r="E7" t="str">
-        <v>Ženatý/Vdaná</v>
+        <v>Rozvedený/á</v>
       </c>
       <c r="F7" t="str">
-        <v>Ano</v>
+        <v>Ne</v>
       </c>
       <c r="G7" t="str">
-        <v>Podnikatel/ka (OSVČ)</v>
+        <v>Zaměstnaný/á</v>
       </c>
       <c r="H7" t="str">
-        <v>Vysoký</v>
+        <v>Střední</v>
       </c>
       <c r="I7" t="str">
-        <v>Praha</v>
+        <v>Plzeňský</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -641,25 +641,25 @@
         <v>P007</v>
       </c>
       <c r="B8">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C8" t="str">
         <v>Muž</v>
       </c>
       <c r="D8" t="str">
-        <v>Vysokoškolské</v>
+        <v>S maturitou</v>
       </c>
       <c r="E8" t="str">
-        <v>Svobodný/á</v>
+        <v>Ženatý/Vdaná</v>
       </c>
       <c r="F8" t="str">
         <v>Ano</v>
       </c>
       <c r="G8" t="str">
-        <v>Zaměstnaný/á</v>
+        <v>Podnikatel/ka (OSVČ)</v>
       </c>
       <c r="H8" t="str">
-        <v>Střední</v>
+        <v>Vysoký</v>
       </c>
       <c r="I8" t="str">
         <v>Jihočeský</v>
@@ -673,13 +673,13 @@
         <v>P008</v>
       </c>
       <c r="B9">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C9" t="str">
-        <v>Muž</v>
+        <v>Žena</v>
       </c>
       <c r="D9" t="str">
-        <v>Základní</v>
+        <v>Vysokoškolské</v>
       </c>
       <c r="E9" t="str">
         <v>Ženatý/Vdaná</v>
@@ -688,13 +688,13 @@
         <v>Ano</v>
       </c>
       <c r="G9" t="str">
-        <v>Důchodce/kyně</v>
+        <v>Mateřská/rodičovská dovolená</v>
       </c>
       <c r="H9" t="str">
-        <v>Nízký</v>
+        <v>Střední</v>
       </c>
       <c r="I9" t="str">
-        <v>Kraj Vysočina</v>
+        <v>Jihomoravský</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -705,13 +705,13 @@
         <v>P009</v>
       </c>
       <c r="B10">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C10" t="str">
-        <v>Žena</v>
+        <v>Muž</v>
       </c>
       <c r="D10" t="str">
-        <v>Vyšší odborné</v>
+        <v>S maturitou</v>
       </c>
       <c r="E10" t="str">
         <v>Svobodný/á</v>
@@ -720,13 +720,13 @@
         <v>Ne</v>
       </c>
       <c r="G10" t="str">
-        <v>Zaměstnaný/á</v>
+        <v>Student/ka</v>
       </c>
       <c r="H10" t="str">
-        <v>Střední</v>
+        <v>Nízký</v>
       </c>
       <c r="I10" t="str">
-        <v>Plzeňský</v>
+        <v>Olomoucký</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -737,28 +737,28 @@
         <v>P010</v>
       </c>
       <c r="B11">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C11" t="str">
         <v>Žena</v>
       </c>
       <c r="D11" t="str">
-        <v>S maturitou</v>
+        <v>Základní</v>
       </c>
       <c r="E11" t="str">
-        <v>Ženatý/Vdaná</v>
+        <v>Rozvedený/á</v>
       </c>
       <c r="F11" t="str">
-        <v>Ano</v>
+        <v>Ne</v>
       </c>
       <c r="G11" t="str">
-        <v>Zaměstnaný/á</v>
+        <v>Nezaměstnaný/á</v>
       </c>
       <c r="H11" t="str">
-        <v>Střední</v>
+        <v>Nízký</v>
       </c>
       <c r="I11" t="str">
-        <v>Olomoucký</v>
+        <v>Ústecký</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -769,28 +769,28 @@
         <v>P011</v>
       </c>
       <c r="B12">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C12" t="str">
         <v>Muž</v>
       </c>
       <c r="D12" t="str">
-        <v>S maturitou</v>
+        <v>Vysokoškolské</v>
       </c>
       <c r="E12" t="str">
-        <v>Svobodný/á</v>
+        <v>Ženatý/Vdaná</v>
       </c>
       <c r="F12" t="str">
-        <v>Ne</v>
+        <v>Ano</v>
       </c>
       <c r="G12" t="str">
         <v>Zaměstnaný/á</v>
       </c>
       <c r="H12" t="str">
-        <v>Spíše nižší</v>
+        <v>Spíše vyšší</v>
       </c>
       <c r="I12" t="str">
-        <v>Liberecký</v>
+        <v>Praha</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -801,7 +801,7 @@
         <v>P012</v>
       </c>
       <c r="B13">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C13" t="str">
         <v>Žena</v>
@@ -816,7 +816,7 @@
         <v>Ano</v>
       </c>
       <c r="G13" t="str">
-        <v>Zaměstnaný/á</v>
+        <v>Důchodce/kyně</v>
       </c>
       <c r="H13" t="str">
         <v>Spíše nižší</v>
@@ -833,28 +833,28 @@
         <v>P013</v>
       </c>
       <c r="B14">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C14" t="str">
-        <v>Muž</v>
+        <v>Žena</v>
       </c>
       <c r="D14" t="str">
-        <v>Vysokoškolské</v>
+        <v>S maturitou</v>
       </c>
       <c r="E14" t="str">
-        <v>Rozvedený/á</v>
+        <v>Svobodný/á</v>
       </c>
       <c r="F14" t="str">
-        <v>Ano</v>
+        <v>Ne</v>
       </c>
       <c r="G14" t="str">
-        <v>Podnikatel/ka (OSVČ)</v>
+        <v>Zaměstnaný/á</v>
       </c>
       <c r="H14" t="str">
-        <v>Spíše vyšší</v>
+        <v>Nízký</v>
       </c>
       <c r="I14" t="str">
-        <v>Královéhradecký</v>
+        <v>Liberecký</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -865,28 +865,28 @@
         <v>P014</v>
       </c>
       <c r="B15">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C15" t="str">
-        <v>Žena</v>
+        <v>Muž</v>
       </c>
       <c r="D15" t="str">
-        <v>S maturitou</v>
+        <v>Vyšší odborné</v>
       </c>
       <c r="E15" t="str">
-        <v>Svobodný/á</v>
+        <v>Ženatý/Vdaná</v>
       </c>
       <c r="F15" t="str">
-        <v>Ne</v>
+        <v>Ano</v>
       </c>
       <c r="G15" t="str">
-        <v>Student/ka</v>
+        <v>Zaměstnaný/á</v>
       </c>
       <c r="H15" t="str">
-        <v>Nízký</v>
+        <v>Střední</v>
       </c>
       <c r="I15" t="str">
-        <v>Pardubický</v>
+        <v>Karlovarský</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -897,28 +897,28 @@
         <v>P015</v>
       </c>
       <c r="B16">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="C16" t="str">
-        <v>Muž</v>
+        <v>Žena</v>
       </c>
       <c r="D16" t="str">
-        <v>Vyučení</v>
+        <v>Vysokoškolské</v>
       </c>
       <c r="E16" t="str">
-        <v>Ženatý/Vdaná</v>
+        <v>Svobodný/á</v>
       </c>
       <c r="F16" t="str">
         <v>Ano</v>
       </c>
       <c r="G16" t="str">
-        <v>Důchodce/kyně</v>
+        <v>Zaměstnaný/á</v>
       </c>
       <c r="H16" t="str">
         <v>Střední</v>
       </c>
       <c r="I16" t="str">
-        <v>Karlovarský</v>
+        <v>Pardubický</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -929,28 +929,28 @@
         <v>P016</v>
       </c>
       <c r="B17">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="C17" t="str">
-        <v>Žena</v>
+        <v>Muž</v>
       </c>
       <c r="D17" t="str">
-        <v>Vysokoškolské</v>
+        <v>S maturitou</v>
       </c>
       <c r="E17" t="str">
-        <v>Svobodný/á</v>
+        <v>Ovdovělý/á</v>
       </c>
       <c r="F17" t="str">
-        <v>Ano</v>
+        <v>Ne</v>
       </c>
       <c r="G17" t="str">
-        <v>Zaměstnaný/á</v>
+        <v>Důchodce/kyně</v>
       </c>
       <c r="H17" t="str">
-        <v>Spíše vyšší</v>
+        <v>Střední</v>
       </c>
       <c r="I17" t="str">
-        <v>Praha</v>
+        <v>Královéhradecký</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -961,13 +961,13 @@
         <v>P017</v>
       </c>
       <c r="B18">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C18" t="str">
-        <v>Muž</v>
+        <v>Žena</v>
       </c>
       <c r="D18" t="str">
-        <v>S maturitou</v>
+        <v>Základní</v>
       </c>
       <c r="E18" t="str">
         <v>Ženatý/Vdaná</v>
@@ -976,13 +976,13 @@
         <v>Ano</v>
       </c>
       <c r="G18" t="str">
-        <v>Zaměstnaný/á</v>
+        <v>Nezaměstnaný/á</v>
       </c>
       <c r="H18" t="str">
-        <v>Střední</v>
+        <v>Nízký</v>
       </c>
       <c r="I18" t="str">
-        <v>Jihomoravský</v>
+        <v>Moravskoslezský</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -993,16 +993,16 @@
         <v>P018</v>
       </c>
       <c r="B19">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C19" t="str">
         <v>Muž</v>
       </c>
       <c r="D19" t="str">
-        <v>Vysokoškolské</v>
+        <v>Vyučení</v>
       </c>
       <c r="E19" t="str">
-        <v>Svobodný/á</v>
+        <v>Rozvedený/á</v>
       </c>
       <c r="F19" t="str">
         <v>Ne</v>
@@ -1011,10 +1011,10 @@
         <v>Zaměstnaný/á</v>
       </c>
       <c r="H19" t="str">
-        <v>Střední</v>
+        <v>Spíše nižší</v>
       </c>
       <c r="I19" t="str">
-        <v>Středočeský</v>
+        <v>Kraj Vysočina</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1025,31 +1025,31 @@
         <v>P019</v>
       </c>
       <c r="B20">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C20" t="str">
         <v>Žena</v>
       </c>
       <c r="D20" t="str">
-        <v>Vyučení</v>
+        <v>S maturitou</v>
       </c>
       <c r="E20" t="str">
-        <v>Rozvedený/á</v>
+        <v>Ženatý/Vdaná</v>
       </c>
       <c r="F20" t="str">
-        <v>Ne</v>
+        <v>Ano</v>
       </c>
       <c r="G20" t="str">
-        <v>Nezaměstnaný/á</v>
+        <v>Podnikatel/ka (OSVČ)</v>
       </c>
       <c r="H20" t="str">
-        <v>Nízký</v>
+        <v>Spíše vyšší</v>
       </c>
       <c r="I20" t="str">
-        <v>Ústecký</v>
+        <v>Jihočeský</v>
       </c>
       <c r="J20" t="str">
-        <v>Po rozvodu zůstala sama se dvěma dětmi. Přišla o práci v továrně před rokem. Aktivně hledá práci, ale na trhu v regionu není mnoho příležitostí.</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1057,28 +1057,28 @@
         <v>P020</v>
       </c>
       <c r="B21">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="C21" t="str">
-        <v>Žena</v>
+        <v>Muž</v>
       </c>
       <c r="D21" t="str">
-        <v>Základní</v>
+        <v>S maturitou</v>
       </c>
       <c r="E21" t="str">
-        <v>Ovdovělý/á</v>
+        <v>Svobodný/á</v>
       </c>
       <c r="F21" t="str">
         <v>Ne</v>
       </c>
       <c r="G21" t="str">
-        <v>Důchodce/kyně</v>
+        <v>Student/ka</v>
       </c>
       <c r="H21" t="str">
         <v>Nízký</v>
       </c>
       <c r="I21" t="str">
-        <v>Moravskoslezský</v>
+        <v>Středočeský</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1093,59 +1093,171 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:D11"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" customWidth="1"/>
+    <col min="4" max="4" width="100.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Pole</v>
+        <v>Sloupec</v>
       </c>
       <c r="B1" t="str">
-        <v>Hodnota</v>
+        <v>Povinné</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Popis</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Povolené hodnoty</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Název</v>
+        <v>ID</v>
       </c>
       <c r="B2" t="str">
-        <v>Vzorová populace Respondex</v>
+        <v>Ano</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Unikátní identifikátor osoby (libovolný řetězec)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>P001, R0001, OSOBA_001, ...</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Popis</v>
+        <v>Věk</v>
       </c>
       <c r="B3" t="str">
-        <v>Ukázková populace 20 osob pokrývající různé demografické skupiny české populace</v>
+        <v>Ano</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Věk v celých letech, rozsah 18–100</v>
+      </c>
+      <c r="D3" t="str">
+        <v>celé číslo 18–100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Zdroj</v>
+        <v>Pohlaví</v>
       </c>
       <c r="B4" t="str">
-        <v>Ručně sestaveno pro demonstraci platformy Respondex</v>
+        <v>Ano</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Pohlaví osoby</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Muž | Žena</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Datum</v>
+        <v>Vzdělání</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-21</v>
+        <v>Ne</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Nejvyšší dosažené vzdělání</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Základní | Vyučení | S maturitou | Vyšší odborné | Vysokoškolské</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Verze</v>
+        <v>Stav</v>
       </c>
       <c r="B6" t="str">
-        <v>1.0</v>
+        <v>Ne</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Rodinný stav</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Svobodný/á | Ženatý/Vdaná | Rozvedený/á | Ovdovělý/á | Registrované partnerství</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Partner</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Ne</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Má aktuálního partnera/partnerku</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Ano | Ne</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Status</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Ne</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Pracovní status</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Zaměstnaný/á | Podnikatel/ka (OSVČ) | Nezaměstnaný/á | Student/ka | Důchodce/kyně | Mateřská/rodičovská dovolená | Jiné</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Příjem</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Ne</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Příjmová skupina</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Nízký | Spíše nižší | Střední | Spíše vyšší | Vysoký</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Kraj</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Ne</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Kraj bydliště</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Praha | Středočeský | Jihočeský | Plzeňský | Karlovarský | Ústecký | Liberecký | Královéhradecký | Pardubický | Kraj Vysočina | Jihomoravský | Olomoucký | Zlínský | Moravskoslezský</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Životní příběh</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Ne</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Volný text s životním příběhem (pro Strategii C — manuální narativ)</v>
+      </c>
+      <c r="D11" t="str">
+        <v>libovolný text</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>